--- a/docs/sample-output/02-podium-mixed-use-2-phase/proforma.xlsx
+++ b/docs/sample-output/02-podium-mixed-use-2-phase/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at -9.77% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at -9.47% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Station Square — podium mixed-use, 2 phases · 5-Year Before-Tax</t>
@@ -1073,7 +1073,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>141426387.37</v>
+        <v>140902626.09</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.041710206762527444</v>
+        <v>0.04186525136239922</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1089,7 +1089,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>50418507.097405</v>
+        <v>50231786.20108499</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>-0.09772194586979613</v>
+        <v>-0.09473231549857163</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1113,7 +1113,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>0.5740798253243224</v>
+        <v>0.5850973387287026</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1129,7 +1129,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>-0.09772194586979613</v>
+        <v>-0.09473231549857163</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>141426387.37</v>
+        <v>140902626.09</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1160,7 +1160,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>919271.517905</v>
+        <v>915867.0695850002</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1168,7 +1168,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>141426387.37</v>
+        <v>140902626.09</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-91927151.7905</v>
+        <v>-91586706.95850001</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1184,7 +1184,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>50418507.097405</v>
+        <v>50231786.20108499</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>15.038960800723098</v>
+        <v>14.98326521586559</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>447.5518587658228</v>
+        <v>445.8943863607595</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>91927151.7905</v>
+        <v>91586706.95850001</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1247,7 +1247,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>620698.7121123729</v>
+        <v>618400.004226271</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1255,7 +1255,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>7448384.545348475</v>
+        <v>7420800.050715251</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1490,19 +1490,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-7448384.545348475</v>
+        <v>-7420800.050715251</v>
       </c>
       <c r="C13" s="16">
-        <v>-7448384.545348475</v>
+        <v>-7420800.050715251</v>
       </c>
       <c r="D13" s="16">
-        <v>-7448384.545348475</v>
+        <v>-7420800.050715251</v>
       </c>
       <c r="E13" s="16">
-        <v>-7448384.545348475</v>
+        <v>-7420800.050715251</v>
       </c>
       <c r="F13" s="16">
-        <v>-7448384.545348475</v>
+        <v>-7420800.050715251</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,19 +1510,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>-1549460.6864684746</v>
+        <v>-1521876.1918352507</v>
       </c>
       <c r="C14" s="18">
-        <v>-1372492.9707020745</v>
+        <v>-1344908.4760688506</v>
       </c>
       <c r="D14" s="18">
-        <v>-1190216.2234626822</v>
+        <v>-1162631.7288294584</v>
       </c>
       <c r="E14" s="18">
-        <v>-1002471.1738061085</v>
+        <v>-974886.6791728847</v>
       </c>
       <c r="F14" s="18">
-        <v>-809093.7726598363</v>
+        <v>-781509.2780266125</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,19 +1666,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-90409343.28093472</v>
+        <v>-90074519.53098701</v>
       </c>
       <c r="C9" s="16">
-        <v>-88789884.32449862</v>
+        <v>-88461058.11087851</v>
       </c>
       <c r="D9" s="16">
-        <v>-87061967.20250791</v>
+        <v>-86739540.19133069</v>
       </c>
       <c r="E9" s="16">
-        <v>-85218328.27075058</v>
+        <v>-84902729.02845518</v>
       </c>
       <c r="F9" s="16">
-        <v>-83251217.42530945</v>
+        <v>-82942903.22022295</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1686,19 +1686,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>14538106.719065279</v>
+        <v>14872930.46901299</v>
       </c>
       <c r="C10" s="18">
-        <v>19305865.675501376</v>
+        <v>19634691.889121488</v>
       </c>
       <c r="D10" s="18">
-        <v>24276132.797492087</v>
+        <v>24598559.808669314</v>
       </c>
       <c r="E10" s="18">
-        <v>29459971.729249418</v>
+        <v>29775570.971544817</v>
       </c>
       <c r="F10" s="18">
-        <v>34867982.57469055</v>
+        <v>35176296.77977705</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1736,19 +1736,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>0.818398885507823</v>
+        <v>0.8153680108896182</v>
       </c>
       <c r="C13" s="21">
-        <v>0.7803303100100947</v>
+        <v>0.777440419307277</v>
       </c>
       <c r="D13" s="21">
-        <v>0.7428622263392543</v>
+        <v>0.7401110956785157</v>
       </c>
       <c r="E13" s="21">
-        <v>0.7059523192898138</v>
+        <v>0.7033378815088157</v>
       </c>
       <c r="F13" s="21">
-        <v>0.6695664765257805</v>
+        <v>0.6670867907944839</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,19 +1756,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>0.7919735914499588</v>
+        <v>0.794917504657929</v>
       </c>
       <c r="C14" s="22">
-        <v>0.8157327991934576</v>
+        <v>0.8187650297976669</v>
       </c>
       <c r="D14" s="22">
-        <v>0.8402047831692614</v>
+        <v>0.8433279806915969</v>
       </c>
       <c r="E14" s="22">
-        <v>0.8654109266643392</v>
+        <v>0.8686278201123449</v>
       </c>
       <c r="F14" s="22">
-        <v>0.8913732544642695</v>
+        <v>0.8946866547157153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,19 +1776,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.06416954886542683</v>
+        <v>0.0644080790190757</v>
       </c>
       <c r="C15" s="21">
-        <v>0.06609463533138965</v>
+        <v>0.06634032138964799</v>
       </c>
       <c r="D15" s="21">
-        <v>0.06807747439133134</v>
+        <v>0.06833053103133743</v>
       </c>
       <c r="E15" s="21">
-        <v>0.07011979862307127</v>
+        <v>0.07038044696227755</v>
       </c>
       <c r="F15" s="21">
-        <v>0.07222339258176343</v>
+        <v>0.07249186037114588</v>
       </c>
     </row>
   </sheetData>
@@ -1864,19 +1864,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>-0.030731982672057817</v>
+        <v>-0.030297074958532507</v>
       </c>
       <c r="C5" s="21">
-        <v>-0.027222007348422967</v>
+        <v>-0.026774052403491896</v>
       </c>
       <c r="D5" s="21">
-        <v>-0.023606732765079068</v>
+        <v>-0.023145339171800065</v>
       </c>
       <c r="E5" s="21">
-        <v>-0.01988299994423486</v>
+        <v>-0.019407764543157485</v>
       </c>
       <c r="F5" s="21">
-        <v>-0.0160475551387653</v>
+        <v>-0.015558062675655604</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,19 +1884,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>-0.10657926210133753</v>
+        <v>-0.10232524081289857</v>
       </c>
       <c r="C6" s="21">
-        <v>-0.07109201906670941</v>
+        <v>-0.068496540901362</v>
       </c>
       <c r="D6" s="21">
-        <v>-0.04902824652473646</v>
+        <v>-0.047264219445063205</v>
       </c>
       <c r="E6" s="21">
-        <v>-0.03402824629362431</v>
+        <v>-0.03274115818314753</v>
       </c>
       <c r="F6" s="21">
-        <v>-0.02320449056456536</v>
+        <v>-0.022216928715358814</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,19 +1904,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>0.25761663286665065</v>
+        <v>0.2657889612710878</v>
       </c>
       <c r="C7" s="23">
-        <v>0.32495829332428</v>
+        <v>0.3338106901891378</v>
       </c>
       <c r="D7" s="23">
-        <v>0.39993177263070284</v>
+        <v>0.40948461059287333</v>
       </c>
       <c r="E7" s="23">
-        <v>0.4828649651957488</v>
+        <v>0.4931393002127271</v>
       </c>
       <c r="F7" s="23">
-        <v>0.5740798253243224</v>
+        <v>0.5850973387287026</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,19 +1924,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>-0.21622565689332313</v>
+        <v>-0.21331222181674653</v>
       </c>
       <c r="C8" s="21">
-        <v>-0.08041154601275544</v>
+        <v>-0.07866429244109271</v>
       </c>
       <c r="D8" s="21">
-        <v>-0.030093973472799726</v>
+        <v>-0.02883849105229252</v>
       </c>
       <c r="E8" s="21">
-        <v>-0.0039310927104198885</v>
+        <v>-0.002943167567464686</v>
       </c>
       <c r="F8" s="21">
-        <v>0.012084473915418134</v>
+        <v>0.012904689018664591</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1964,19 +1964,19 @@
         <v>80</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.7423833671333326</v>
+        <v>-0.7342110387291791</v>
       </c>
       <c r="C10" s="24">
-        <v>-0.4187703245016001</v>
+        <v>-0.4115449893323472</v>
       </c>
       <c r="D10" s="24">
-        <v>-0.2509623894772779</v>
+        <v>-0.24572863047062868</v>
       </c>
       <c r="E10" s="24">
-        <v>-0.1563106335814315</v>
+        <v>-0.15243191148155444</v>
       </c>
       <c r="F10" s="24">
-        <v>-0.09772194586979613</v>
+        <v>-0.09473231549857163</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1984,19 +1984,19 @@
         <v>81</v>
       </c>
       <c r="B11" s="21">
-        <v>-0.5262</v>
+        <v>-0.5208999999999999</v>
       </c>
       <c r="C11" s="21">
-        <v>-0.33840000000000003</v>
+        <v>-0.3328</v>
       </c>
       <c r="D11" s="21">
-        <v>-0.2209</v>
+        <v>-0.2169</v>
       </c>
       <c r="E11" s="21">
-        <v>-0.1524</v>
+        <v>-0.14950000000000002</v>
       </c>
       <c r="F11" s="21">
-        <v>-0.1098</v>
+        <v>-0.1076</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2090,19 +2090,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>127283749</v>
+        <v>126812363</v>
       </c>
       <c r="C6" s="18">
-        <v>134355068</v>
+        <v>133857495</v>
       </c>
       <c r="D6" s="18">
-        <v>141426387</v>
+        <v>140902626</v>
       </c>
       <c r="E6" s="18">
-        <v>148497707</v>
+        <v>147947757</v>
       </c>
       <c r="F6" s="18">
-        <v>155569026</v>
+        <v>154992889</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,19 +2110,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.046344674046959446</v>
+        <v>0.04651694613466039</v>
       </c>
       <c r="C7" s="21">
-        <v>0.04390548080315065</v>
+        <v>0.044068685574012875</v>
       </c>
       <c r="D7" s="21">
-        <v>0.04171020687164977</v>
+        <v>0.041865251389140185</v>
       </c>
       <c r="E7" s="21">
-        <v>0.03972400637054955</v>
+        <v>0.03987166807050681</v>
       </c>
       <c r="F7" s="21">
-        <v>0.03791836981019602</v>
+        <v>0.03805931934645079</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2130,19 +2130,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>82734436.85000001</v>
+        <v>82428035.95</v>
       </c>
       <c r="C8" s="16">
-        <v>87330794.2</v>
+        <v>87007371.75</v>
       </c>
       <c r="D8" s="16">
-        <v>91927151.55</v>
+        <v>91586706.9</v>
       </c>
       <c r="E8" s="16">
-        <v>96523509.55</v>
+        <v>96166042.05</v>
       </c>
       <c r="F8" s="16">
-        <v>101119866.9</v>
+        <v>100745377.85000001</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2150,19 +2150,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>45376656.518499985</v>
+        <v>45208607.4095</v>
       </c>
       <c r="C9" s="16">
-        <v>47897581.742</v>
+        <v>47720196.9675</v>
       </c>
       <c r="D9" s="16">
-        <v>50418506.96550001</v>
+        <v>50231786.169</v>
       </c>
       <c r="E9" s="16">
-        <v>52939432.545499995</v>
+        <v>52743375.37050001</v>
       </c>
       <c r="F9" s="16">
-        <v>55460357.768999994</v>
+        <v>55254964.92849998</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2170,19 +2170,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.046344674046959446</v>
+        <v>0.04651694613466039</v>
       </c>
       <c r="C10" s="21">
-        <v>0.04390548080315065</v>
+        <v>0.044068685574012875</v>
       </c>
       <c r="D10" s="21">
-        <v>0.04171020687164977</v>
+        <v>0.041865251389140185</v>
       </c>
       <c r="E10" s="21">
-        <v>0.03972400637054955</v>
+        <v>0.03987166807050681</v>
       </c>
       <c r="F10" s="21">
-        <v>0.03791836981019602</v>
+        <v>0.03805931934645079</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2190,19 +2190,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.04773501426836823</v>
+        <v>0.0479124545187002</v>
       </c>
       <c r="C11" s="21">
-        <v>0.04522264522724517</v>
+        <v>0.04539074614123326</v>
       </c>
       <c r="D11" s="21">
-        <v>0.04296151307779927</v>
+        <v>0.04312120893081439</v>
       </c>
       <c r="E11" s="21">
-        <v>0.04091572656166603</v>
+        <v>0.041067818112622015</v>
       </c>
       <c r="F11" s="21">
-        <v>0.039055920904501905</v>
+        <v>0.03920109892684431</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,19 +2210,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.04916706469641928</v>
+        <v>0.04934982815426121</v>
       </c>
       <c r="C12" s="21">
-        <v>0.046579324584062526</v>
+        <v>0.046752468525470256</v>
       </c>
       <c r="D12" s="21">
-        <v>0.04425035847013325</v>
+        <v>0.044414845198738825</v>
       </c>
       <c r="E12" s="21">
-        <v>0.042143198358516015</v>
+        <v>0.042299852656000676</v>
       </c>
       <c r="F12" s="21">
-        <v>0.04022759853163696</v>
+        <v>0.04037713189464965</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2230,19 +2230,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.05064207663731186</v>
+        <v>0.050830322998889045</v>
       </c>
       <c r="C13" s="21">
-        <v>0.0479767043215844</v>
+        <v>0.04815504258123437</v>
       </c>
       <c r="D13" s="21">
-        <v>0.04557786922423725</v>
+        <v>0.04574729055470099</v>
       </c>
       <c r="E13" s="21">
-        <v>0.043407494309271495</v>
+        <v>0.0435688482356807</v>
       </c>
       <c r="F13" s="21">
-        <v>0.04143442648758607</v>
+        <v>0.04158844585148914</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2250,19 +2250,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.05216133893643122</v>
+        <v>0.052355232688855724</v>
       </c>
       <c r="C14" s="21">
-        <v>0.04941600545123195</v>
+        <v>0.049599693858671405</v>
       </c>
       <c r="D14" s="21">
-        <v>0.04694520530096437</v>
+        <v>0.04711970927134203</v>
       </c>
       <c r="E14" s="21">
-        <v>0.04470971913854965</v>
+        <v>0.04487591368275112</v>
       </c>
       <c r="F14" s="21">
-        <v>0.04267745928221366</v>
+        <v>0.04283609922703382</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2270,19 +2270,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>-0.017732074440832014</v>
+        <v>-0.01724884277827676</v>
       </c>
       <c r="C15" s="21">
-        <v>-0.024574131225709398</v>
+        <v>-0.024116333831986483</v>
       </c>
       <c r="D15" s="21">
-        <v>-0.03073198236596431</v>
+        <v>-0.030297074883522755</v>
       </c>
       <c r="E15" s="21">
-        <v>-0.036303372270873775</v>
+        <v>-0.03588917395402309</v>
       </c>
       <c r="F15" s="21">
-        <v>-0.0413682714584012</v>
+        <v>-0.040972901090225174</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,19 +2290,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>-0.013832101870260387</v>
+        <v>-0.013334373257828476</v>
       </c>
       <c r="C16" s="21">
-        <v>-0.020879420358684096</v>
+        <v>-0.020407889043149496</v>
       </c>
       <c r="D16" s="21">
-        <v>-0.027222007033146655</v>
+        <v>-0.026774052326231854</v>
       </c>
       <c r="E16" s="21">
-        <v>-0.0329605386352034</v>
+        <v>-0.0325339143688472</v>
       </c>
       <c r="F16" s="21">
-        <v>-0.03817738479835665</v>
+        <v>-0.037770153319135344</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2310,19 +2310,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>-0.00981513012257161</v>
+        <v>-0.009302469651766744</v>
       </c>
       <c r="C17" s="21">
-        <v>-0.017073868165648032</v>
+        <v>-0.016588190910647393</v>
       </c>
       <c r="D17" s="21">
-        <v>-0.02360673244034447</v>
+        <v>-0.023145339092222224</v>
       </c>
       <c r="E17" s="21">
-        <v>-0.02951741999046292</v>
+        <v>-0.029077996996116035</v>
       </c>
       <c r="F17" s="21">
-        <v>-0.034890771538510765</v>
+        <v>-0.03447132311491282</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2330,19 +2330,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>-0.0056776492224521755</v>
+        <v>-0.005149608937523166</v>
       </c>
       <c r="C18" s="21">
-        <v>-0.013154149406820893</v>
+        <v>-0.012653901834170233</v>
       </c>
       <c r="D18" s="21">
-        <v>-0.019882999609758225</v>
+        <v>-0.01940776446119231</v>
       </c>
       <c r="E18" s="21">
-        <v>-0.025971007786380226</v>
+        <v>-0.025518402102202936</v>
       </c>
       <c r="F18" s="21">
-        <v>-0.031505559880869505</v>
+        <v>-0.03107352800456362</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2350,19 +2350,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>-0.0014160438953291306</v>
+        <v>-0.0008721624018522516</v>
       </c>
       <c r="C19" s="21">
-        <v>-0.009116839085228912</v>
+        <v>-0.008601584085398732</v>
       </c>
       <c r="D19" s="21">
-        <v>-0.016047554794254366</v>
+        <v>-0.015558062591231473</v>
       </c>
       <c r="E19" s="21">
-        <v>-0.022318203216175028</v>
+        <v>-0.021852019361472422</v>
       </c>
       <c r="F19" s="21">
-        <v>-0.028018791873498986</v>
+        <v>-0.027573799040903922</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2370,19 +2370,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>-0.12913962128151485</v>
+        <v>-0.12590246537001273</v>
       </c>
       <c r="C20" s="21">
-        <v>-0.17497437566759266</v>
+        <v>-0.17190760323983345</v>
       </c>
       <c r="D20" s="21">
-        <v>-0.21622565484290143</v>
+        <v>-0.21331222131484567</v>
       </c>
       <c r="E20" s="21">
-        <v>-0.25354824597445835</v>
+        <v>-0.2507735425897356</v>
       </c>
       <c r="F20" s="21">
-        <v>-0.2874778694127482</v>
+        <v>-0.2848292939498724</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2390,19 +2390,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>-0.029451192395749344</v>
+        <v>-0.027604843752668605</v>
       </c>
       <c r="C21" s="21">
-        <v>-0.05595323149321439</v>
+        <v>-0.0541584488073374</v>
       </c>
       <c r="D21" s="21">
-        <v>-0.08041154478199139</v>
+        <v>-0.07866429214015547</v>
       </c>
       <c r="E21" s="21">
-        <v>-0.10307529999428638</v>
+        <v>-0.10137203907578353</v>
       </c>
       <c r="F21" s="21">
-        <v>-0.1241531612351888</v>
+        <v>-0.12249077832895461</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2410,19 +2410,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>0.006243920682979273</v>
+        <v>0.007549900275283709</v>
       </c>
       <c r="C22" s="21">
-        <v>-0.012582297707170304</v>
+        <v>-0.011302523520393447</v>
       </c>
       <c r="D22" s="21">
-        <v>-0.03009397258809928</v>
+        <v>-0.02883849083642137</v>
       </c>
       <c r="E22" s="21">
-        <v>-0.04644301079257868</v>
+        <v>-0.045210137148944764</v>
       </c>
       <c r="F22" s="21">
-        <v>-0.06175747807261969</v>
+        <v>-0.06054572626510535</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2430,19 +2430,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>0.024564019901885205</v>
+        <v>0.02558440308005956</v>
       </c>
       <c r="C23" s="21">
-        <v>0.00982634793993807</v>
+        <v>0.010829893610355265</v>
       </c>
       <c r="D23" s="21">
-        <v>-0.003931092014228171</v>
+        <v>-0.0029431673975178494</v>
       </c>
       <c r="E23" s="21">
-        <v>-0.016818976021369447</v>
+        <v>-0.01584560206598022</v>
       </c>
       <c r="F23" s="21">
-        <v>-0.02893084705960794</v>
+        <v>-0.027971080664007757</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2450,19 +2450,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.03570005793701042</v>
+        <v>0.03654412605369557</v>
       </c>
       <c r="C24" s="21">
-        <v>0.023496880034428097</v>
+        <v>0.024328567438200423</v>
       </c>
       <c r="D24" s="21">
-        <v>0.012084474493793984</v>
+        <v>0.012904689160172775</v>
       </c>
       <c r="E24" s="21">
-        <v>0.0013744768030251146</v>
+        <v>0.0021840157464204603</v>
       </c>
       <c r="F24" s="21">
-        <v>-0.008707865329264906</v>
+        <v>-0.007908301866486358</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2470,19 +2470,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>-0.49810276233102324</v>
+        <v>-0.48902238109363716</v>
       </c>
       <c r="C25" s="21">
-        <v>-0.6266714983383049</v>
+        <v>-0.6180690511343812</v>
       </c>
       <c r="D25" s="21">
-        <v>-0.7423833613815034</v>
+        <v>-0.734211037319672</v>
       </c>
       <c r="E25" s="21">
-        <v>-0.8470750616114802</v>
+        <v>-0.8392918824115344</v>
       </c>
       <c r="F25" s="21">
-        <v>-0.9422493209053334</v>
+        <v>-0.9348199367169696</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2490,19 +2490,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>-0.2295216759828355</v>
+        <v>-0.22330525698696294</v>
       </c>
       <c r="C26" s="21">
-        <v>-0.32306696730212936</v>
+        <v>-0.31644384679355864</v>
       </c>
       <c r="D26" s="21">
-        <v>-0.41877031938705456</v>
+        <v>-0.4115449880935538</v>
       </c>
       <c r="E26" s="21">
-        <v>-0.5199675524695992</v>
+        <v>-0.5117858950306083</v>
       </c>
       <c r="F26" s="21">
-        <v>-0.6330549317679689</v>
+        <v>-0.6231194685437715</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,19 +2510,19 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>-0.11593718653957487</v>
+        <v>-0.11158291245848481</v>
       </c>
       <c r="C27" s="21">
-        <v>-0.18210740452449703</v>
+        <v>-0.17738355265758984</v>
       </c>
       <c r="D27" s="21">
-        <v>-0.25096238577077923</v>
+        <v>-0.24572862957385797</v>
       </c>
       <c r="E27" s="21">
-        <v>-0.32466679243704877</v>
+        <v>-0.31869100765251673</v>
       </c>
       <c r="F27" s="21">
-        <v>-0.40688183996114724</v>
+        <v>-0.3997270973285677</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2530,19 +2530,19 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>-0.05578998709982326</v>
+        <v>-0.05254162520182999</v>
       </c>
       <c r="C28" s="21">
-        <v>-0.10513359754717559</v>
+        <v>-0.10161391868422406</v>
       </c>
       <c r="D28" s="21">
-        <v>-0.1563106308354173</v>
+        <v>-0.15243191081637938</v>
       </c>
       <c r="E28" s="21">
-        <v>-0.2105956329266056</v>
+        <v>-0.20622384320553291</v>
       </c>
       <c r="F28" s="21">
-        <v>-0.2699197330557127</v>
+        <v>-0.26483191802076167</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2550,19 +2550,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>-0.01954129126151081</v>
+        <v>-0.016995860677460325</v>
       </c>
       <c r="C29" s="21">
-        <v>-0.05808050503971508</v>
+        <v>-0.055340441157657086</v>
       </c>
       <c r="D29" s="21">
-        <v>-0.09772194375394183</v>
+        <v>-0.09473231498566555</v>
       </c>
       <c r="E29" s="21">
-        <v>-0.13923682891287992</v>
+        <v>-0.13591897440306136</v>
       </c>
       <c r="F29" s="21">
-        <v>-0.18369174330962346</v>
+        <v>-0.17992605600758804</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sample-output/02-podium-mixed-use-2-phase/proforma.xlsx
+++ b/docs/sample-output/02-podium-mixed-use-2-phase/proforma.xlsx
@@ -264,7 +264,7 @@
     <t>Leverage Impact</t>
   </si>
   <si>
-    <t>Optimal holding period: Year 5 at -9.47% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
+    <t>Optimal holding period: Year 5 at -9.61% equity IRR. Leverage is positive when the equity IRR exceeds the property IRR.</t>
   </si>
   <si>
     <t>Acquisition-Price Sensitivity   ·   Station Square — podium mixed-use, 2 phases · 5-Year Before-Tax</t>
@@ -1073,7 +1073,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="6">
-        <v>140902626.09</v>
+        <v>141142303.95</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="7">
-        <v>0.04186525136239922</v>
+        <v>0.0417941587588772</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1089,7 +1089,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="6">
-        <v>50231786.20108499</v>
+        <v>50317231.35817498</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>-0.09473231549857163</v>
+        <v>-0.09609916012199057</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1113,7 +1113,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="8">
-        <v>0.5850973387287026</v>
+        <v>0.5800454780840629</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1129,7 +1129,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="7">
-        <v>-0.09473231549857163</v>
+        <v>-0.09609916012199057</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1144,7 +1144,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="6">
-        <v>140902626.09</v>
+        <v>141142303.95</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1160,7 +1160,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="6">
-        <v>915867.0695850002</v>
+        <v>917424.975675</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1168,7 +1168,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="6">
-        <v>140902626.09</v>
+        <v>141142303.95</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="6">
-        <v>-91586706.95850001</v>
+        <v>-91742497.5675</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1184,7 +1184,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="10">
-        <v>50231786.20108499</v>
+        <v>50317231.35817498</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="11">
-        <v>14.98326521586559</v>
+        <v>15.008752015099956</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="12">
-        <v>445.8943863607595</v>
+        <v>446.6528606012658</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1215,7 +1215,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="6">
-        <v>91586706.95850001</v>
+        <v>91742497.5675</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1247,7 +1247,7 @@
         <v>42</v>
       </c>
       <c r="B35" s="12">
-        <v>618400.004226271</v>
+        <v>619451.9135749459</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1255,7 +1255,7 @@
         <v>43</v>
       </c>
       <c r="B36" s="6">
-        <v>7420800.050715251</v>
+        <v>7433422.962899351</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1490,19 +1490,19 @@
         <v>60</v>
       </c>
       <c r="B13" s="16">
-        <v>-7420800.050715251</v>
+        <v>-7433422.962899351</v>
       </c>
       <c r="C13" s="16">
-        <v>-7420800.050715251</v>
+        <v>-7433422.962899351</v>
       </c>
       <c r="D13" s="16">
-        <v>-7420800.050715251</v>
+        <v>-7433422.962899351</v>
       </c>
       <c r="E13" s="16">
-        <v>-7420800.050715251</v>
+        <v>-7433422.962899351</v>
       </c>
       <c r="F13" s="16">
-        <v>-7420800.050715251</v>
+        <v>-7433422.962899351</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1510,19 +1510,19 @@
         <v>61</v>
       </c>
       <c r="B14" s="18">
-        <v>-1521876.1918352507</v>
+        <v>-1534499.1040193504</v>
       </c>
       <c r="C14" s="18">
-        <v>-1344908.4760688506</v>
+        <v>-1357531.3882529503</v>
       </c>
       <c r="D14" s="18">
-        <v>-1162631.7288294584</v>
+        <v>-1175254.641013558</v>
       </c>
       <c r="E14" s="18">
-        <v>-974886.6791728847</v>
+        <v>-987509.5913569843</v>
       </c>
       <c r="F14" s="18">
-        <v>-781509.2780266125</v>
+        <v>-794132.1902107121</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,19 +1666,19 @@
         <v>68</v>
       </c>
       <c r="B9" s="16">
-        <v>-90074519.53098701</v>
+        <v>-90227737.88241734</v>
       </c>
       <c r="C9" s="16">
-        <v>-88461058.11087851</v>
+        <v>-88611531.9358859</v>
       </c>
       <c r="D9" s="16">
-        <v>-86739540.19133069</v>
+        <v>-86887085.68389773</v>
       </c>
       <c r="E9" s="16">
-        <v>-84902729.02845518</v>
+        <v>-85047150.07273507</v>
       </c>
       <c r="F9" s="16">
-        <v>-82942903.22022295</v>
+        <v>-83083990.56612743</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1686,19 +1686,19 @@
         <v>69</v>
       </c>
       <c r="B10" s="18">
-        <v>14872930.46901299</v>
+        <v>14719712.117582664</v>
       </c>
       <c r="C10" s="18">
-        <v>19634691.889121488</v>
+        <v>19484218.064114094</v>
       </c>
       <c r="D10" s="18">
-        <v>24598559.808669314</v>
+        <v>24451014.316102266</v>
       </c>
       <c r="E10" s="18">
-        <v>29775570.971544817</v>
+        <v>29631149.92726493</v>
       </c>
       <c r="F10" s="18">
-        <v>35176296.77977705</v>
+        <v>35035209.433872566</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1736,19 +1736,19 @@
         <v>71</v>
       </c>
       <c r="B13" s="21">
-        <v>0.8153680108896182</v>
+        <v>0.8167549663026255</v>
       </c>
       <c r="C13" s="21">
-        <v>0.777440419307277</v>
+        <v>0.7787628592159416</v>
       </c>
       <c r="D13" s="21">
-        <v>0.7401110956785157</v>
+        <v>0.7413700377472119</v>
       </c>
       <c r="E13" s="21">
-        <v>0.7033378815088157</v>
+        <v>0.7045342716895726</v>
       </c>
       <c r="F13" s="21">
-        <v>0.6670867907944839</v>
+        <v>0.6682215172285375</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1756,19 +1756,19 @@
         <v>72</v>
       </c>
       <c r="B14" s="22">
-        <v>0.794917504657929</v>
+        <v>0.7935676320750042</v>
       </c>
       <c r="C14" s="22">
-        <v>0.8187650297976669</v>
+        <v>0.8173746610372544</v>
       </c>
       <c r="D14" s="22">
-        <v>0.8433279806915969</v>
+        <v>0.8418959008683721</v>
       </c>
       <c r="E14" s="22">
-        <v>0.8686278201123449</v>
+        <v>0.8671527778944232</v>
       </c>
       <c r="F14" s="22">
-        <v>0.8946866547157153</v>
+        <v>0.8931673612312562</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,19 +1776,19 @@
         <v>73</v>
       </c>
       <c r="B15" s="21">
-        <v>0.0644080790190757</v>
+        <v>0.064298705782888</v>
       </c>
       <c r="C15" s="21">
-        <v>0.06634032138964799</v>
+        <v>0.06622766695637464</v>
       </c>
       <c r="D15" s="21">
-        <v>0.06833053103133743</v>
+        <v>0.06821449696506589</v>
       </c>
       <c r="E15" s="21">
-        <v>0.07038044696227755</v>
+        <v>0.07026093187401786</v>
       </c>
       <c r="F15" s="21">
-        <v>0.07249186037114588</v>
+        <v>0.07236875983023841</v>
       </c>
     </row>
   </sheetData>
@@ -1864,19 +1864,19 @@
         <v>75</v>
       </c>
       <c r="B5" s="21">
-        <v>-0.030297074958532507</v>
+        <v>-0.030496493201230997</v>
       </c>
       <c r="C5" s="21">
-        <v>-0.026774052403491896</v>
+        <v>-0.02697945319347134</v>
       </c>
       <c r="D5" s="21">
-        <v>-0.023145339171800065</v>
+        <v>-0.023356901985478892</v>
       </c>
       <c r="E5" s="21">
-        <v>-0.019407764543157485</v>
+        <v>-0.019625674241246678</v>
       </c>
       <c r="F5" s="21">
-        <v>-0.015558062675655604</v>
+        <v>-0.015782509664687472</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1884,19 +1884,19 @@
         <v>76</v>
       </c>
       <c r="B6" s="21">
-        <v>-0.10232524081289857</v>
+        <v>-0.1042479018449277</v>
       </c>
       <c r="C6" s="21">
-        <v>-0.068496540901362</v>
+        <v>-0.0696733830316364</v>
       </c>
       <c r="D6" s="21">
-        <v>-0.047264219445063205</v>
+        <v>-0.0480656804588917</v>
       </c>
       <c r="E6" s="21">
-        <v>-0.03274115818314753</v>
+        <v>-0.03332673871182884</v>
       </c>
       <c r="F6" s="21">
-        <v>-0.022216928715358814</v>
+        <v>-0.022666688826553247</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,19 +1904,19 @@
         <v>77</v>
       </c>
       <c r="B7" s="23">
-        <v>0.2657889612710878</v>
+        <v>0.2620417033621451</v>
       </c>
       <c r="C7" s="23">
-        <v>0.3338106901891378</v>
+        <v>0.3297516004752531</v>
       </c>
       <c r="D7" s="23">
-        <v>0.40948461059287333</v>
+        <v>0.4051043476084399</v>
       </c>
       <c r="E7" s="23">
-        <v>0.4931393002127271</v>
+        <v>0.4884282091691278</v>
       </c>
       <c r="F7" s="23">
-        <v>0.5850973387287026</v>
+        <v>0.5800454780840629</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,19 +1924,19 @@
         <v>78</v>
       </c>
       <c r="B8" s="21">
-        <v>-0.21331222181674653</v>
+        <v>-0.21464811926164887</v>
       </c>
       <c r="C8" s="21">
-        <v>-0.07866429244109271</v>
+        <v>-0.07946507677252762</v>
       </c>
       <c r="D8" s="21">
-        <v>-0.02883849105229252</v>
+        <v>-0.029413804904906797</v>
       </c>
       <c r="E8" s="21">
-        <v>-0.002943167567464686</v>
+        <v>-0.0033958446703828762</v>
       </c>
       <c r="F8" s="21">
-        <v>0.012904689018664591</v>
+        <v>0.01252887166708061</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1964,19 +1964,19 @@
         <v>80</v>
       </c>
       <c r="B10" s="24">
-        <v>-0.7342110387291791</v>
+        <v>-0.7379582966381856</v>
       </c>
       <c r="C10" s="24">
-        <v>-0.4115449893323472</v>
+        <v>-0.4148478779293927</v>
       </c>
       <c r="D10" s="24">
-        <v>-0.24572863047062868</v>
+        <v>-0.2481204871255659</v>
       </c>
       <c r="E10" s="24">
-        <v>-0.15243191148155444</v>
+        <v>-0.15420480649837287</v>
       </c>
       <c r="F10" s="24">
-        <v>-0.09473231549857163</v>
+        <v>-0.09609916012199057</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1984,19 +1984,19 @@
         <v>81</v>
       </c>
       <c r="B11" s="21">
-        <v>-0.5208999999999999</v>
+        <v>-0.5234</v>
       </c>
       <c r="C11" s="21">
-        <v>-0.3328</v>
+        <v>-0.3353</v>
       </c>
       <c r="D11" s="21">
-        <v>-0.2169</v>
+        <v>-0.21869999999999998</v>
       </c>
       <c r="E11" s="21">
-        <v>-0.14950000000000002</v>
+        <v>-0.15080000000000002</v>
       </c>
       <c r="F11" s="21">
-        <v>-0.1076</v>
+        <v>-0.1086</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2090,19 +2090,19 @@
         <v>18</v>
       </c>
       <c r="B6" s="18">
-        <v>126812363</v>
+        <v>127028074</v>
       </c>
       <c r="C6" s="18">
-        <v>133857495</v>
+        <v>134085189</v>
       </c>
       <c r="D6" s="18">
-        <v>140902626</v>
+        <v>141142304</v>
       </c>
       <c r="E6" s="18">
-        <v>147947757</v>
+        <v>148199419</v>
       </c>
       <c r="F6" s="18">
-        <v>154992889</v>
+        <v>155256534</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,19 +2110,19 @@
         <v>19</v>
       </c>
       <c r="B7" s="21">
-        <v>0.04651694613466039</v>
+        <v>0.046437954013850515</v>
       </c>
       <c r="C7" s="21">
-        <v>0.044068685574012875</v>
+        <v>0.04399385124392822</v>
       </c>
       <c r="D7" s="21">
-        <v>0.041865251389140185</v>
+        <v>0.04179415874407152</v>
       </c>
       <c r="E7" s="21">
-        <v>0.03987166807050681</v>
+        <v>0.039803960762356295</v>
       </c>
       <c r="F7" s="21">
-        <v>0.03805931934645079</v>
+        <v>0.03799468986522654</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2130,19 +2130,19 @@
         <v>90</v>
       </c>
       <c r="B8" s="16">
-        <v>82428035.95</v>
+        <v>82568248.10000001</v>
       </c>
       <c r="C8" s="16">
-        <v>87007371.75</v>
+        <v>87155372.85000001</v>
       </c>
       <c r="D8" s="16">
-        <v>91586706.9</v>
+        <v>91742497.60000001</v>
       </c>
       <c r="E8" s="16">
-        <v>96166042.05</v>
+        <v>96329622.35000001</v>
       </c>
       <c r="F8" s="16">
-        <v>100745377.85000001</v>
+        <v>100916747.10000001</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2150,19 +2150,19 @@
         <v>20</v>
       </c>
       <c r="B9" s="16">
-        <v>45208607.4095</v>
+        <v>45285508.381</v>
       </c>
       <c r="C9" s="16">
-        <v>47720196.9675</v>
+        <v>47801369.8785</v>
       </c>
       <c r="D9" s="16">
-        <v>50231786.169</v>
+        <v>50317231.376</v>
       </c>
       <c r="E9" s="16">
-        <v>52743375.37050001</v>
+        <v>52833092.873500004</v>
       </c>
       <c r="F9" s="16">
-        <v>55254964.92849998</v>
+        <v>55348954.37099998</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2170,19 +2170,19 @@
         <v>91</v>
       </c>
       <c r="B10" s="21">
-        <v>0.04651694613466039</v>
+        <v>0.046437954013850515</v>
       </c>
       <c r="C10" s="21">
-        <v>0.044068685574012875</v>
+        <v>0.04399385124392822</v>
       </c>
       <c r="D10" s="21">
-        <v>0.041865251389140185</v>
+        <v>0.04179415874407152</v>
       </c>
       <c r="E10" s="21">
-        <v>0.03987166807050681</v>
+        <v>0.039803960762356295</v>
       </c>
       <c r="F10" s="21">
-        <v>0.03805931934645079</v>
+        <v>0.03799468986522654</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2190,19 +2190,19 @@
         <v>92</v>
       </c>
       <c r="B11" s="21">
-        <v>0.0479124545187002</v>
+        <v>0.047831092634266034</v>
       </c>
       <c r="C11" s="21">
-        <v>0.04539074614123326</v>
+        <v>0.04531366678124606</v>
       </c>
       <c r="D11" s="21">
-        <v>0.04312120893081439</v>
+        <v>0.04304798350639366</v>
       </c>
       <c r="E11" s="21">
-        <v>0.041067818112622015</v>
+        <v>0.040998079585226985</v>
       </c>
       <c r="F11" s="21">
-        <v>0.03920109892684431</v>
+        <v>0.03913453056118334</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2210,19 +2210,19 @@
         <v>93</v>
       </c>
       <c r="B12" s="21">
-        <v>0.04934982815426121</v>
+        <v>0.049266025413294015</v>
       </c>
       <c r="C12" s="21">
-        <v>0.046752468525470256</v>
+        <v>0.04667307678468345</v>
       </c>
       <c r="D12" s="21">
-        <v>0.044414845198738825</v>
+        <v>0.04433942301158547</v>
       </c>
       <c r="E12" s="21">
-        <v>0.042299852656000676</v>
+        <v>0.042228021972783795</v>
       </c>
       <c r="F12" s="21">
-        <v>0.04037713189464965</v>
+        <v>0.040308566478018844</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2230,19 +2230,19 @@
         <v>94</v>
       </c>
       <c r="B13" s="21">
-        <v>0.050830322998889045</v>
+        <v>0.050744006175692837</v>
       </c>
       <c r="C13" s="21">
-        <v>0.04815504258123437</v>
+        <v>0.04807326908822395</v>
       </c>
       <c r="D13" s="21">
-        <v>0.04574729055470099</v>
+        <v>0.045669605701933035</v>
       </c>
       <c r="E13" s="21">
-        <v>0.0435688482356807</v>
+        <v>0.04349486263196731</v>
       </c>
       <c r="F13" s="21">
-        <v>0.04158844585148914</v>
+        <v>0.041517823472359404</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2250,19 +2250,19 @@
         <v>95</v>
       </c>
       <c r="B14" s="21">
-        <v>0.052355232688855724</v>
+        <v>0.05226632636096363</v>
       </c>
       <c r="C14" s="21">
-        <v>0.049599693858671405</v>
+        <v>0.04951546716087068</v>
       </c>
       <c r="D14" s="21">
-        <v>0.04711970927134203</v>
+        <v>0.04703969387299104</v>
       </c>
       <c r="E14" s="21">
-        <v>0.04487591368275112</v>
+        <v>0.04479970851092634</v>
       </c>
       <c r="F14" s="21">
-        <v>0.04283609922703382</v>
+        <v>0.042763358176530195</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2270,19 +2270,19 @@
         <v>96</v>
       </c>
       <c r="B15" s="21">
-        <v>-0.01724884277827676</v>
+        <v>-0.017470419554742055</v>
       </c>
       <c r="C15" s="21">
-        <v>-0.024116333831986483</v>
+        <v>-0.024326247801368394</v>
       </c>
       <c r="D15" s="21">
-        <v>-0.030297074883522755</v>
+        <v>-0.030496493242761668</v>
       </c>
       <c r="E15" s="21">
-        <v>-0.03588917395402309</v>
+        <v>-0.03607909627702599</v>
       </c>
       <c r="F15" s="21">
-        <v>-0.040972901090225174</v>
+        <v>-0.04115418995761435</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2290,19 +2290,19 @@
         <v>97</v>
       </c>
       <c r="B16" s="21">
-        <v>-0.013334373257828476</v>
+        <v>-0.013562597337587733</v>
       </c>
       <c r="C16" s="21">
-        <v>-0.020407889043149496</v>
+        <v>-0.020624100431612863</v>
       </c>
       <c r="D16" s="21">
-        <v>-0.026774052326231854</v>
+        <v>-0.02697945323624793</v>
       </c>
       <c r="E16" s="21">
-        <v>-0.0325339143688472</v>
+        <v>-0.03272953436154019</v>
       </c>
       <c r="F16" s="21">
-        <v>-0.037770153319135344</v>
+        <v>-0.03795688085254619</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2310,19 +2310,19 @@
         <v>98</v>
       </c>
       <c r="B17" s="21">
-        <v>-0.009302469651766744</v>
+        <v>-0.009537540453918776</v>
       </c>
       <c r="C17" s="21">
-        <v>-0.016588190910647393</v>
+        <v>-0.01681088864076466</v>
       </c>
       <c r="D17" s="21">
-        <v>-0.023145339092222224</v>
+        <v>-0.023356902029538783</v>
       </c>
       <c r="E17" s="21">
-        <v>-0.029077996996116035</v>
+        <v>-0.029279485588589806</v>
       </c>
       <c r="F17" s="21">
-        <v>-0.03447132311491282</v>
+        <v>-0.03466365247432599</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2330,19 +2330,19 @@
         <v>99</v>
       </c>
       <c r="B18" s="21">
-        <v>-0.005149608937523166</v>
+        <v>-0.005391731863739759</v>
       </c>
       <c r="C18" s="21">
-        <v>-0.012653901834170233</v>
+        <v>-0.012883280496191021</v>
       </c>
       <c r="D18" s="21">
-        <v>-0.01940776446119231</v>
+        <v>-0.019625674286628366</v>
       </c>
       <c r="E18" s="21">
-        <v>-0.025518402102202936</v>
+        <v>-0.02572593535245092</v>
       </c>
       <c r="F18" s="21">
-        <v>-0.03107352800456362</v>
+        <v>-0.03127162724475919</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2350,19 +2350,19 @@
         <v>100</v>
       </c>
       <c r="B19" s="21">
-        <v>-0.0008721624018522516</v>
+        <v>-0.001121549015855342</v>
       </c>
       <c r="C19" s="21">
-        <v>-0.008601584085398732</v>
+        <v>-0.008837844107280144</v>
       </c>
       <c r="D19" s="21">
-        <v>-0.015558062591231473</v>
+        <v>-0.015782509711430612</v>
       </c>
       <c r="E19" s="21">
-        <v>-0.021852019361472422</v>
+        <v>-0.022065778609227843</v>
       </c>
       <c r="F19" s="21">
-        <v>-0.027573799040903922</v>
+        <v>-0.027777841258305357</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2370,19 +2370,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="21">
-        <v>-0.12590246537001273</v>
+        <v>-0.12738680223663917</v>
       </c>
       <c r="C20" s="21">
-        <v>-0.17190760323983345</v>
+        <v>-0.1733138112747622</v>
       </c>
       <c r="D20" s="21">
-        <v>-0.21331222131484567</v>
+        <v>-0.2146481195395212</v>
       </c>
       <c r="E20" s="21">
-        <v>-0.2507735425897356</v>
+        <v>-0.2520458271242061</v>
       </c>
       <c r="F20" s="21">
-        <v>-0.2848292939498724</v>
+        <v>-0.2860437431969315</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2390,19 +2390,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21">
-        <v>-0.027604843752668605</v>
+        <v>-0.028451047528989304</v>
       </c>
       <c r="C21" s="21">
-        <v>-0.0541584488073374</v>
+        <v>-0.05498101718365317</v>
       </c>
       <c r="D21" s="21">
-        <v>-0.07866429214015547</v>
+        <v>-0.07946507693902552</v>
       </c>
       <c r="E21" s="21">
-        <v>-0.10137203907578353</v>
+        <v>-0.10215266052823876</v>
       </c>
       <c r="F21" s="21">
-        <v>-0.12249077832895461</v>
+        <v>-0.12325266342400631</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2410,19 +2410,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="21">
-        <v>0.007549900275283709</v>
+        <v>0.00695144355256762</v>
       </c>
       <c r="C22" s="21">
-        <v>-0.011302523520393447</v>
+        <v>-0.011888969900272214</v>
       </c>
       <c r="D22" s="21">
-        <v>-0.02883849083642137</v>
+        <v>-0.029413805024776286</v>
       </c>
       <c r="E22" s="21">
-        <v>-0.045210137148944764</v>
+        <v>-0.04577508998718167</v>
       </c>
       <c r="F22" s="21">
-        <v>-0.06054572626510535</v>
+        <v>-0.06110099880299383</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2430,19 +2430,19 @@
         <v>104</v>
       </c>
       <c r="B23" s="21">
-        <v>0.02558440308005956</v>
+        <v>0.025116850478570315</v>
       </c>
       <c r="C23" s="21">
-        <v>0.010829893610355265</v>
+        <v>0.010370057943673643</v>
       </c>
       <c r="D23" s="21">
-        <v>-0.0029431673975178494</v>
+        <v>-0.0033958447649274307</v>
       </c>
       <c r="E23" s="21">
-        <v>-0.01584560206598022</v>
+        <v>-0.016291610847355663</v>
       </c>
       <c r="F23" s="21">
-        <v>-0.027971080664007757</v>
+        <v>-0.02841085300035972</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2450,19 +2450,19 @@
         <v>105</v>
       </c>
       <c r="B24" s="21">
-        <v>0.03654412605369557</v>
+        <v>0.036157376529377505</v>
       </c>
       <c r="C24" s="21">
-        <v>0.024328567438200423</v>
+        <v>0.02394749243275475</v>
       </c>
       <c r="D24" s="21">
-        <v>0.012904689160172775</v>
+        <v>0.012528871588555798</v>
       </c>
       <c r="E24" s="21">
-        <v>0.0021840157464204603</v>
+        <v>0.0018130910234146428</v>
       </c>
       <c r="F24" s="21">
-        <v>-0.007908301866486358</v>
+        <v>-0.008274654606404332</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2470,19 +2470,19 @@
         <v>106</v>
       </c>
       <c r="B25" s="21">
-        <v>-0.48902238109363716</v>
+        <v>-0.49318601886724406</v>
       </c>
       <c r="C25" s="21">
-        <v>-0.6180690511343812</v>
+        <v>-0.62201353370212</v>
       </c>
       <c r="D25" s="21">
-        <v>-0.734211037319672</v>
+        <v>-0.7379582974184548</v>
       </c>
       <c r="E25" s="21">
-        <v>-0.8392918824115344</v>
+        <v>-0.8428607029835397</v>
       </c>
       <c r="F25" s="21">
-        <v>-0.9348199367169696</v>
+        <v>-0.9382265264701268</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2490,19 +2490,19 @@
         <v>107</v>
       </c>
       <c r="B26" s="21">
-        <v>-0.22330525698696294</v>
+        <v>-0.2261500253046906</v>
       </c>
       <c r="C26" s="21">
-        <v>-0.31644384679355864</v>
+        <v>-0.31947343009627593</v>
       </c>
       <c r="D26" s="21">
-        <v>-0.4115449880935538</v>
+        <v>-0.41484787861905636</v>
       </c>
       <c r="E26" s="21">
-        <v>-0.5117858950306083</v>
+        <v>-0.5155217302304068</v>
       </c>
       <c r="F26" s="21">
-        <v>-0.6231194685437715</v>
+        <v>-0.6276452218542887</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2510,19 +2510,19 @@
         <v>108</v>
       </c>
       <c r="B27" s="21">
-        <v>-0.11158291245848481</v>
+        <v>-0.11357484687105535</v>
       </c>
       <c r="C27" s="21">
-        <v>-0.17738355265758984</v>
+        <v>-0.17954365123242016</v>
       </c>
       <c r="D27" s="21">
-        <v>-0.24572862957385797</v>
+        <v>-0.24812048762523997</v>
       </c>
       <c r="E27" s="21">
-        <v>-0.31869100765251673</v>
+        <v>-0.3214195345255726</v>
       </c>
       <c r="F27" s="21">
-        <v>-0.3997270973285677</v>
+        <v>-0.40298897536477607</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2530,19 +2530,19 @@
         <v>109</v>
       </c>
       <c r="B28" s="21">
-        <v>-0.05254162520182999</v>
+        <v>-0.05402763737293176</v>
       </c>
       <c r="C28" s="21">
-        <v>-0.10161391868422406</v>
+        <v>-0.10322346929456766</v>
       </c>
       <c r="D28" s="21">
-        <v>-0.15243191081637938</v>
+        <v>-0.15420480686924026</v>
       </c>
       <c r="E28" s="21">
-        <v>-0.20622384320553291</v>
+        <v>-0.20822077947071896</v>
       </c>
       <c r="F28" s="21">
-        <v>-0.26483191802076167</v>
+        <v>-0.2671535993233636</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2550,19 +2550,19 @@
         <v>110</v>
       </c>
       <c r="B29" s="21">
-        <v>-0.016995860677460325</v>
+        <v>-0.018160417432592463</v>
       </c>
       <c r="C29" s="21">
-        <v>-0.055340441157657086</v>
+        <v>-0.05659366514432097</v>
       </c>
       <c r="D29" s="21">
-        <v>-0.09473231498566555</v>
+        <v>-0.09609916040734914</v>
       </c>
       <c r="E29" s="21">
-        <v>-0.13591897440306136</v>
+        <v>-0.13743511708647832</v>
       </c>
       <c r="F29" s="21">
-        <v>-0.17992605600758804</v>
+        <v>-0.1816456452212496</v>
       </c>
     </row>
   </sheetData>
